--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -979,7 +979,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Fragments, written once per release. Voice-neutral: no we or our, no artist name in the hook or making line.</t>
+          <t>Fragments, written once per release. No we or our: the sheet adds our where a line needs it.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>1 to 2 sentences about the work only. Reused in every post and email.</t>
+          <t>2 to 3 sentences about the work. Write it as editorially as you like; the one test is that it must read as well in the middle of an email as at the top of a post. Self-contained, no rhetorical question. It reaches 16 slots, so it is the one fragment that must stand alone.</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4637,142 +4637,154 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Naming the work</t>
+          <t>The hook carries the voice</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>The opener's tail is the title (single print only), the edition phrase, and the qualifier if one is written: 'The Changeling, a new limited edition print'; 'a quartet of new limited edition prints spanning five decades of the artist's career'; 'six new limited edition prints from his iconic Dream House series'. A pair or a quartet takes no title; the hook names the work. The same tail is used by the Insiders email, LE early access, Now Live and the Monthly Preview paragraph.</t>
+          <t>The hook is where a release sounds like itself, and it can be as editorial as the writer likes: 'Folklore says a changeling is a child swapped at birth for something not quite human. Grayson Perry's version is the generation raised by screens, and he means it to disturb.' The one test is that it must read as well in the middle of an email as at the top of a post, because it appears in 16 slots and most of them are middle paragraphs. That rules out a sentence which assumes it is opening: a rhetorical question, or an aside about the artist that never describes the work.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Fragments</t>
+          <t>Naming the work</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Four per release, written once: bio (2 to 3 sentences, Coming Soon only), hook (1 to 2 sentences about the work, in every post and email), making (one sentence on how it was made), quote (verbatim). The hook and bio must not repeat each other.</t>
+          <t>The opener's tail is the title (single print only), the edition phrase, and the qualifier if one is written: 'The Changeling, a new limited edition print'; 'a quartet of new limited edition prints spanning five decades of the artist's career'; 'six new limited edition prints from his iconic Dream House series'. A pair or a quartet takes no title; the hook names the work. The same tail is used by the Insiders email, LE early access, Now Live and the Monthly Preview paragraph.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Voice</t>
+          <t>Fragments</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Fragments are voice-neutral: no we or our, no artist name in the hook or the making line, and 'printmakers at Make-Ready' where it applies. The sheet adds 'our'. The Insiders email and the first-time survey are signed by the advisor named on Inputs. Features never say 'our'.</t>
+          <t>Four per release, written once: bio (2 to 3 sentences, Coming Soon only), hook (2 to 3 sentences about the work, in every post and email), making (one sentence on how it was made), quote (verbatim). The hook and bio must not repeat each other.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Who and what</t>
+          <t>Voice</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>'by {artist}' is always the artist. 'collaboration with {collab_with}' is the artist's name, or the estate. 'unit' is what one is called (print, embroidery, sculpture), and the sheet writes 'a print' or 'an embroidery' wherever a line names one.</t>
+          <t>Fragments never say we or our, and the making line says 'printmakers at Make-Ready' so the sheet can add 'our'. The hook may name the artist. The Insiders email and the first-time survey are signed by the advisor named on Inputs. Features never say 'our'.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Who and what</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>The standard three (signed by the artist, individually numbered, free worldwide shipping) plus anything bespoke: framed, a set offer, a partner credit. One line of short sentences in a post, a list in an email. The beneficiary follows, named once.</t>
+          <t>'by {artist}' is always the artist. 'collaboration with {collab_with}' is the artist's name, or the estate. 'unit' is what one is called (print, embroidery, sculpture), and the sheet writes 'a print' or 'an embroidery' wherever a line names one.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Beneficiary</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>One phrase everywhere: 'released in support of'. It goes in the opener unless the hook already names the beneficiary.</t>
+          <t>The standard three (signed by the artist, individually numbered, free worldwide shipping) plus anything bespoke: framed, a set offer, a partner credit. One line of short sentences in a post, a list in an email. The beneficiary follows, named once.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Framing offer</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>A framing code on Inputs adds the first-purchase framing line to Early Access, Now Live, 3 days to go and Last chance. Blank means no offer.</t>
+          <t>One phrase everywhere: 'released in support of'. It goes in the opener unless the hook already names the beneficiary.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Action lines</t>
+          <t>Framing offer</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Three CTAs: get updates before launch, enter the draw for a draw, buy one for an open window. One deadline form: Closes {date} at {time} UK time, or 'until {time} on {weekday}, {date}' in an email.</t>
+          <t>A framing code on Inputs adds the first-purchase framing line to Early Access, Now Live, 3 days to go and Last chance. Blank means no offer.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Mechanic and window</t>
+          <t>Action lines</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Set mechanic to timed or draw and the sheet switches every line. For a timed edition, a 48-hour window gets the halfway email; a one-week window gets 5 days to go and 3 days to go.</t>
+          <t>Three CTAs: get updates before launch, enter the draw for a draw, buy one for an open window. One deadline form: Closes {date} at {time} UK time, or 'until {time} on {weekday}, {date}' in an email.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Mechanic and window</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Enter launch and close once as date and time; the sheet derives '30 April', '14:00 UK time', 'Thursday' and '07 May' where each email needs them.</t>
+          <t>Set mechanic to timed or draw and the sheet switches every line. For a timed edition, a 48-hour window gets the halfway email; a one-week window gets 5 days to go and 3 days to go.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>What stays written</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>A delay reason, a framing paragraph, editorial deep dives, the rest of the Monthly Preview, the artist's own email, artist-local times, and anything for a second release.</t>
+          <t>Enter launch and close once as date and time; the sheet derives '30 April', '14:00 UK time', 'Thursday' and '07 May' where each email needs them.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
+          <t>What stays written</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>A delay reason, a framing paragraph, editorial deep dives, the rest of the Monthly Preview, the artist's own email, artist-local times, and anything for a second release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
           <t>How to use</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Fill the blue cells on Inputs. Read Posts, Tweets and Emails. To change the house wording, edit the blue cells on Lines once.</t>
         </is>
